--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F92C10E-D2B7-47B1-8FA1-D0AD108D22B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE395C92-7955-4865-B9D6-5E10FF3D96E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -69,6 +69,18 @@
   </si>
   <si>
     <t>Datalab cluster setup and reseraching code</t>
+  </si>
+  <si>
+    <t>Trying to get the TUvpn to run but the westbahn Internet was too slow</t>
+  </si>
+  <si>
+    <t>Cisco Secure Client (TU VPN), lets go finally im able to connect to slurmcluster from @home</t>
+  </si>
+  <si>
+    <t>10:00-?</t>
+  </si>
+  <si>
+    <t>Cisco Secure Client (TU VPN) setup on pc, conda setup, looking into spike_gpt.py, found some improvements</t>
   </si>
 </sst>
 </file>
@@ -104,10 +116,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -442,11 +453,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -457,7 +471,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -537,11 +551,44 @@
       <c r="A9" s="1">
         <v>46100</v>
       </c>
-      <c r="B9" s="2">
-        <v>0.41666666666666669</v>
+      <c r="B9">
+        <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\UNI\6\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE395C92-7955-4865-B9D6-5E10FF3D96E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1431C0D-D37F-460E-8543-91295ABE23A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -77,10 +77,7 @@
     <t>Cisco Secure Client (TU VPN), lets go finally im able to connect to slurmcluster from @home</t>
   </si>
   <si>
-    <t>10:00-?</t>
-  </si>
-  <si>
-    <t>Cisco Secure Client (TU VPN) setup on pc, conda setup, looking into spike_gpt.py, found some improvements</t>
+    <t>Cisco Secure Client (TU VPN) setup on pc, conda setup, looking into spike_gpt.py, found some improvements, whyyy tf does spike_gpt not work on windows haha</t>
   </si>
 </sst>
 </file>
@@ -454,12 +451,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,7 +467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -481,7 +478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -492,7 +489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -503,7 +500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -514,7 +511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -525,7 +522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -536,7 +533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -547,7 +544,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -558,7 +555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -569,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -580,15 +577,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
         <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\UNI\6\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1431C0D-D37F-460E-8543-91295ABE23A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD3D899-B7F6-4044-9F4A-F025CAAEE506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Date</t>
   </si>
@@ -78,6 +78,21 @@
   </si>
   <si>
     <t>Cisco Secure Client (TU VPN) setup on pc, conda setup, looking into spike_gpt.py, found some improvements, whyyy tf does spike_gpt not work on windows haha</t>
+  </si>
+  <si>
+    <t>setup WSL and Ubuntu on PC, Teamviewer, finally spikegpt py runs, read about embeddings</t>
+  </si>
+  <si>
+    <t>changed embedding in learned session adapter to coordinate aware adapter</t>
+  </si>
+  <si>
+    <t>TODO:</t>
+  </si>
+  <si>
+    <t>LearnedSessionAdapter constructor nimmt parameter die noch nicht aktiv übergeben werden</t>
+  </si>
+  <si>
+    <t>Deswegen würde ich vorher das allen institute dataset exploren wollen (mit jupyter notebook)</t>
   </si>
 </sst>
 </file>
@@ -450,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -588,6 +603,49 @@
         <v>13</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B13">
+        <v>1.5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B14">
+        <v>1.5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f>SUM(B3:B14)</f>
+        <v>22.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\UNI\6\BA Arbeit\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD3D899-B7F6-4044-9F4A-F025CAAEE506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9567E4E-F90B-40C8-92D5-ED1955D2CE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Deswegen würde ich vorher das allen institute dataset exploren wollen (mit jupyter notebook)</t>
+  </si>
+  <si>
+    <t>allen institute dataset testing</t>
   </si>
 </sst>
 </file>
@@ -465,13 +468,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,7 +485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -493,7 +496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -504,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -515,7 +518,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -526,7 +529,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -537,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -548,7 +551,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -559,7 +562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -570,7 +573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -581,7 +584,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -592,7 +595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -603,7 +606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -614,7 +617,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -625,24 +628,35 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>46108</v>
+      </c>
       <c r="B15">
-        <f>SUM(B3:B14)</f>
-        <v>22.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <f>SUM(B3:B15)</f>
+        <v>22.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\UNI\6\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9567E4E-F90B-40C8-92D5-ED1955D2CE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49447E1-ED4A-4BC6-AEEC-CB6999C28EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>Date</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>allen institute dataset testing</t>
+  </si>
+  <si>
+    <t>investigated https://ai.meta.com/blog/tribe-v2-brain-predictive-foundation-model/</t>
   </si>
 </sst>
 </file>
@@ -149,6 +152,896 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$Q$3:$Q$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14.25</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22.25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>22.75</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>25.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-763E-4023-86F9-14E06696920F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1239777983"/>
+        <c:axId val="1239777023"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1239777983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1239777023"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1239777023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1239777983"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>61912</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagramm 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C6F493F-70F8-9D90-6011-CEB115A086BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -468,13 +1361,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,7 +1378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -496,7 +1389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -506,8 +1399,12 @@
       <c r="C3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f>B3</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -517,8 +1414,12 @@
       <c r="C4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f>B3+B4</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -528,8 +1429,12 @@
       <c r="C5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f>Q4+B5</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -539,8 +1444,12 @@
       <c r="C6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" ref="Q6:Q16" si="0">Q5+B6</f>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -550,8 +1459,12 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -561,8 +1474,12 @@
       <c r="C8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -572,8 +1489,12 @@
       <c r="C9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -583,8 +1504,12 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -594,8 +1519,12 @@
       <c r="C11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -605,8 +1534,12 @@
       <c r="C12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>19.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -616,8 +1549,12 @@
       <c r="C13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>20.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -627,8 +1564,12 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>22.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46108</v>
       </c>
@@ -638,29 +1579,49 @@
       <c r="C15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q15">
+        <f t="shared" si="0"/>
+        <v>22.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46111</v>
+      </c>
       <c r="B16">
-        <f>SUM(B3:B15)</f>
-        <v>22.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="0"/>
+        <v>25.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>SUM(B3:B16)</f>
+        <v>25.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7385AB8-5FA0-4937-82A1-66EDD51147E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0255816F-77C1-463B-B8E1-CAD62E702E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="28800" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="28800" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>Date</t>
   </si>
@@ -480,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -570,7 +570,7 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q18" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q19" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
@@ -755,23 +755,38 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46114</v>
+      </c>
       <c r="B19">
-        <f>SUM(B3:B18)</f>
-        <v>29.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="0"/>
+        <v>30.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <f>SUM(B3:B19)</f>
+        <v>30.75</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0255816F-77C1-463B-B8E1-CAD62E702E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3370EFEE-F594-4B01-89FE-16490A36F38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="28800" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>Date</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>implementing the transformer</t>
+  </si>
+  <si>
+    <t>gpt implementation</t>
   </si>
 </sst>
 </file>
@@ -480,13 +483,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,7 +503,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -514,7 +517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -529,7 +532,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -544,7 +547,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -559,7 +562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -570,11 +573,11 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q19" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q21" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -589,7 +592,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -604,7 +607,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -619,7 +622,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -634,7 +637,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -649,7 +652,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -664,7 +667,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -679,7 +682,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -694,7 +697,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46108</v>
       </c>
@@ -709,7 +712,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46111</v>
       </c>
@@ -724,7 +727,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46112</v>
       </c>
@@ -739,7 +742,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46113</v>
       </c>
@@ -754,7 +757,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46114</v>
       </c>
@@ -769,24 +772,39 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>46118</v>
+      </c>
       <c r="B20">
-        <f>SUM(B3:B19)</f>
-        <v>30.75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="0"/>
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <f>SUM(B3:B20)</f>
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3370EFEE-F594-4B01-89FE-16490A36F38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A59E9A-6D86-4890-91E5-E4F86D26228F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="28800" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Date</t>
   </si>
@@ -483,13 +483,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,7 +503,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -532,7 +532,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -547,7 +547,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -562,7 +562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -577,7 +577,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -592,7 +592,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -607,7 +607,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -637,7 +637,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -652,7 +652,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -667,7 +667,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -682,7 +682,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -697,7 +697,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46108</v>
       </c>
@@ -712,7 +712,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46111</v>
       </c>
@@ -727,7 +727,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46112</v>
       </c>
@@ -742,7 +742,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46113</v>
       </c>
@@ -757,7 +757,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46114</v>
       </c>
@@ -772,7 +772,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46118</v>
       </c>
@@ -787,24 +787,39 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46119</v>
+      </c>
       <c r="B21">
-        <f>SUM(B3:B20)</f>
-        <v>31.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+        <v>1.5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="0"/>
+        <v>32.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f>SUM(B3:B21)</f>
+        <v>32.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A59E9A-6D86-4890-91E5-E4F86D26228F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3112CD86-3A4C-4583-BDFE-157B6C357F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="28800" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="5772" yWindow="0" windowWidth="17280" windowHeight="8964" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>Date</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>gpt implementation</t>
+  </si>
+  <si>
+    <t>make spike-gpt runable with datacluster dataset. Damn thats hard i can't seem to get it right</t>
   </si>
 </sst>
 </file>
@@ -483,13 +486,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,7 +506,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -517,7 +520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -532,7 +535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -547,7 +550,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -562,7 +565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -577,7 +580,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -592,7 +595,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -607,7 +610,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -622,7 +625,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -637,7 +640,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -652,7 +655,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -667,7 +670,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -682,7 +685,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -697,7 +700,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46108</v>
       </c>
@@ -712,7 +715,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46111</v>
       </c>
@@ -727,7 +730,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46112</v>
       </c>
@@ -742,7 +745,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46113</v>
       </c>
@@ -757,7 +760,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46114</v>
       </c>
@@ -772,7 +775,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46118</v>
       </c>
@@ -787,7 +790,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46119</v>
       </c>
@@ -802,24 +805,35 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46125</v>
+      </c>
       <c r="B22">
-        <f>SUM(B3:B21)</f>
-        <v>32.75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <f>SUM(B3:B22)</f>
+        <v>38.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3112CD86-3A4C-4583-BDFE-157B6C357F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B5239D-E918-45F4-8AFA-179FFFBF6EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5772" yWindow="0" windowWidth="17280" windowHeight="8964" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="2115" yWindow="2115" windowWidth="28800" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>make spike-gpt runable with datacluster dataset. Damn thats hard i can't seem to get it right</t>
+  </si>
+  <si>
+    <t>finally spike-gpt runnable with sbatch</t>
   </si>
 </sst>
 </file>
@@ -486,13 +489,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,7 +509,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -520,7 +523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -535,7 +538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -550,7 +553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -565,7 +568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -576,11 +579,11 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q21" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q24" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -595,7 +598,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -610,7 +613,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -625,7 +628,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -640,7 +643,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -655,7 +658,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -670,7 +673,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -685,7 +688,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -700,7 +703,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46108</v>
       </c>
@@ -715,7 +718,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46111</v>
       </c>
@@ -730,7 +733,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46112</v>
       </c>
@@ -745,7 +748,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46113</v>
       </c>
@@ -760,7 +763,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46114</v>
       </c>
@@ -775,7 +778,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46118</v>
       </c>
@@ -790,7 +793,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46119</v>
       </c>
@@ -805,7 +808,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46125</v>
       </c>
@@ -815,25 +818,44 @@
       <c r="C22" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q22">
+        <f t="shared" si="0"/>
+        <v>38.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46126</v>
+      </c>
       <c r="B23">
-        <f>SUM(B3:B22)</f>
-        <v>38.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+        <v>1.5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="0"/>
+        <v>40.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f>SUM(B3:B23)</f>
+        <v>40.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B5239D-E918-45F4-8AFA-179FFFBF6EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBBB37D-292B-4B24-BA05-4C9D5B70DF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="2115" windowWidth="28800" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="1752" yWindow="1908" windowWidth="17280" windowHeight="8964" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -116,7 +116,7 @@
     <t>make spike-gpt runable with datacluster dataset. Damn thats hard i can't seem to get it right</t>
   </si>
   <si>
-    <t>finally spike-gpt runnable with sbatch</t>
+    <t>finally spike-gpt runnable with sbatch, 1_default_gpt also runable</t>
   </si>
 </sst>
 </file>
@@ -490,12 +490,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
   <dimension ref="A1:Q29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,7 +509,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -523,7 +523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -538,7 +538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -553,7 +553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -568,7 +568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -579,11 +579,11 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q24" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q23" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -598,7 +598,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -613,7 +613,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -628,7 +628,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -643,7 +643,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -658,7 +658,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -673,7 +673,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -688,7 +688,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -703,7 +703,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46108</v>
       </c>
@@ -718,7 +718,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46111</v>
       </c>
@@ -733,7 +733,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46112</v>
       </c>
@@ -748,7 +748,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46113</v>
       </c>
@@ -763,7 +763,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46114</v>
       </c>
@@ -778,7 +778,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46118</v>
       </c>
@@ -793,7 +793,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46119</v>
       </c>
@@ -808,7 +808,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46125</v>
       </c>
@@ -823,38 +823,38 @@
         <v>38.75</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46126</v>
       </c>
       <c r="B23">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
       </c>
       <c r="Q23">
         <f t="shared" si="0"/>
-        <v>40.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <v>42.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B24">
         <f>SUM(B3:B23)</f>
-        <v>40.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+        <v>42.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>18</v>
       </c>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBBB37D-292B-4B24-BA05-4C9D5B70DF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A6B8B1-BB71-4E6A-A4A6-42A0A5CF4F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1752" yWindow="1908" windowWidth="17280" windowHeight="8964" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="7740" yWindow="2175" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>Date</t>
   </si>
@@ -117,6 +117,15 @@
   </si>
   <si>
     <t>finally spike-gpt runnable with sbatch, 1_default_gpt also runable</t>
+  </si>
+  <si>
+    <t>running 1_default_gpt on compute cluster</t>
+  </si>
+  <si>
+    <t>setting everything up for debute run of 1_default_gpt on cluster, testeing out sbatch script with small parameters on lightweight gpu</t>
+  </si>
+  <si>
+    <t>rerunning script for longer</t>
   </si>
 </sst>
 </file>
@@ -489,13 +498,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,7 +518,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -523,7 +532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -538,7 +547,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -553,7 +562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -568,7 +577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -579,11 +588,11 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q23" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q26" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -598,7 +607,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -613,7 +622,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -628,7 +637,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -643,7 +652,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -658,7 +667,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -673,7 +682,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -688,7 +697,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -703,7 +712,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46108</v>
       </c>
@@ -718,7 +727,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46111</v>
       </c>
@@ -733,7 +742,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46112</v>
       </c>
@@ -748,7 +757,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46113</v>
       </c>
@@ -763,7 +772,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46114</v>
       </c>
@@ -778,7 +787,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46118</v>
       </c>
@@ -793,7 +802,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46119</v>
       </c>
@@ -808,7 +817,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46125</v>
       </c>
@@ -823,7 +832,7 @@
         <v>38.75</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46126</v>
       </c>
@@ -838,24 +847,69 @@
         <v>42.75</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46127</v>
+      </c>
       <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="0"/>
+        <v>44.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="0"/>
+        <v>45.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="0"/>
+        <v>46.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B27">
         <f>SUM(B3:B23)</f>
         <v>42.75</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A6B8B1-BB71-4E6A-A4A6-42A0A5CF4F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09115F29-81FC-4A28-B366-FE23E13B5FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7740" yWindow="2175" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="8085" yWindow="2520" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>Date</t>
   </si>
@@ -126,6 +126,12 @@
   </si>
   <si>
     <t>rerunning script for longer</t>
+  </si>
+  <si>
+    <t>evaluating script</t>
+  </si>
+  <si>
+    <t>redrawing performance plots, progress report to prof</t>
   </si>
 </sst>
 </file>
@@ -498,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -588,7 +594,7 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q26" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q28" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
@@ -882,34 +888,64 @@
         <v>46129</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
         <v>29</v>
       </c>
       <c r="Q26">
         <f t="shared" si="0"/>
-        <v>46.75</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46130</v>
+      </c>
       <c r="B27">
-        <f>SUM(B3:B23)</f>
-        <v>42.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="0"/>
+        <v>51.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="0"/>
+        <v>52.75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <f>SUM(B3:B28)</f>
+        <v>52.75</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09115F29-81FC-4A28-B366-FE23E13B5FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E50784-49DD-450C-B23F-87A50291572E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8085" yWindow="2520" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>redrawing performance plots, progress report to prof</t>
+  </si>
+  <si>
+    <t>discussion with prof, looked into latent space analysis</t>
   </si>
 </sst>
 </file>
@@ -504,13 +507,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,7 +527,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -538,7 +541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -553,7 +556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -568,7 +571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -583,7 +586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -598,7 +601,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -613,7 +616,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -628,7 +631,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -643,7 +646,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -658,7 +661,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -673,7 +676,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -688,7 +691,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -703,7 +706,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -718,7 +721,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46108</v>
       </c>
@@ -733,7 +736,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46111</v>
       </c>
@@ -748,7 +751,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46112</v>
       </c>
@@ -763,7 +766,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46113</v>
       </c>
@@ -778,7 +781,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46114</v>
       </c>
@@ -793,7 +796,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46118</v>
       </c>
@@ -808,7 +811,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46119</v>
       </c>
@@ -823,7 +826,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46125</v>
       </c>
@@ -838,7 +841,7 @@
         <v>38.75</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46126</v>
       </c>
@@ -853,7 +856,7 @@
         <v>42.75</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46127</v>
       </c>
@@ -868,7 +871,7 @@
         <v>44.75</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46128</v>
       </c>
@@ -883,7 +886,7 @@
         <v>45.75</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46129</v>
       </c>
@@ -898,7 +901,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46130</v>
       </c>
@@ -913,7 +916,7 @@
         <v>51.75</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46131</v>
       </c>
@@ -928,24 +931,35 @@
         <v>52.75</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>46132</v>
+      </c>
       <c r="B29">
-        <f>SUM(B3:B28)</f>
-        <v>52.75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <f>SUM(B3:B29)</f>
+        <v>53.75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E50784-49DD-450C-B23F-87A50291572E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C02BBA-E140-43C6-814E-598597E65932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="0" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>discussion with prof, looked into latent space analysis</t>
+  </si>
+  <si>
+    <t>What is a Brain FID</t>
   </si>
 </sst>
 </file>
@@ -507,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="1"/>
@@ -597,7 +600,7 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q28" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q30" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
@@ -941,25 +944,44 @@
       <c r="C29" t="s">
         <v>32</v>
       </c>
+      <c r="Q29">
+        <f t="shared" si="0"/>
+        <v>53.75</v>
+      </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>46155</v>
+      </c>
       <c r="B30">
-        <f>SUM(B3:B29)</f>
-        <v>53.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="0"/>
+        <v>56.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <f>SUM(B3:B30)</f>
+        <v>56.75</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C02BBA-E140-43C6-814E-598597E65932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B2675E-E0B4-49C0-99C6-30D6BED75A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>Date</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>What is a Brain FID</t>
+  </si>
+  <si>
+    <t>Implement Brain FID</t>
   </si>
 </sst>
 </file>
@@ -510,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="1"/>
@@ -600,7 +603,7 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q30" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q31" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
@@ -965,23 +968,38 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>46156</v>
+      </c>
       <c r="B31">
-        <f>SUM(B3:B30)</f>
-        <v>56.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="0"/>
+        <v>60.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <f>SUM(B3:B31)</f>
+        <v>60.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B2675E-E0B4-49C0-99C6-30D6BED75A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466A92D9-EEB8-4318-828E-207D43F3AC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="8430" yWindow="2865" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>Date</t>
   </si>
@@ -514,12 +514,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,7 +533,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -547,7 +547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -562,7 +562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -577,7 +577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -592,7 +592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -603,11 +603,11 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q31" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q32" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -622,7 +622,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -652,7 +652,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -667,7 +667,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -682,7 +682,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -697,7 +697,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -712,7 +712,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -727,7 +727,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46108</v>
       </c>
@@ -742,7 +742,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46111</v>
       </c>
@@ -757,7 +757,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46112</v>
       </c>
@@ -772,7 +772,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46113</v>
       </c>
@@ -787,7 +787,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46114</v>
       </c>
@@ -802,7 +802,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46118</v>
       </c>
@@ -817,7 +817,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46119</v>
       </c>
@@ -832,7 +832,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46125</v>
       </c>
@@ -847,7 +847,7 @@
         <v>38.75</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46126</v>
       </c>
@@ -862,7 +862,7 @@
         <v>42.75</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46127</v>
       </c>
@@ -877,7 +877,7 @@
         <v>44.75</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46128</v>
       </c>
@@ -892,7 +892,7 @@
         <v>45.75</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46129</v>
       </c>
@@ -907,7 +907,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46130</v>
       </c>
@@ -922,7 +922,7 @@
         <v>51.75</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46131</v>
       </c>
@@ -937,7 +937,7 @@
         <v>52.75</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46132</v>
       </c>
@@ -952,7 +952,7 @@
         <v>53.75</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46155</v>
       </c>
@@ -967,7 +967,7 @@
         <v>56.75</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46156</v>
       </c>
@@ -982,23 +982,38 @@
         <v>60.75</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q32">
+        <f t="shared" si="0"/>
+        <v>61.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B37">
-        <f>SUM(B3:B31)</f>
-        <v>60.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <f>SUM(B3:B32)</f>
+        <v>61.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>18</v>
       </c>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466A92D9-EEB8-4318-828E-207D43F3AC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B62A39-3ED1-43B8-BE76-770EF672A314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8430" yWindow="2865" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -514,12 +514,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,7 +533,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -547,7 +547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -562,7 +562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -577,7 +577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -592,7 +592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -607,7 +607,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -622,7 +622,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -652,7 +652,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -667,7 +667,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -682,7 +682,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -697,7 +697,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -712,7 +712,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -727,7 +727,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46108</v>
       </c>
@@ -742,7 +742,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46111</v>
       </c>
@@ -757,7 +757,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46112</v>
       </c>
@@ -772,7 +772,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46113</v>
       </c>
@@ -787,7 +787,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46114</v>
       </c>
@@ -802,7 +802,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46118</v>
       </c>
@@ -817,7 +817,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46119</v>
       </c>
@@ -832,7 +832,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46125</v>
       </c>
@@ -847,7 +847,7 @@
         <v>38.75</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46126</v>
       </c>
@@ -862,7 +862,7 @@
         <v>42.75</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46127</v>
       </c>
@@ -877,7 +877,7 @@
         <v>44.75</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46128</v>
       </c>
@@ -892,7 +892,7 @@
         <v>45.75</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46129</v>
       </c>
@@ -907,7 +907,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46130</v>
       </c>
@@ -922,7 +922,7 @@
         <v>51.75</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46131</v>
       </c>
@@ -937,7 +937,7 @@
         <v>52.75</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46132</v>
       </c>
@@ -952,7 +952,7 @@
         <v>53.75</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46155</v>
       </c>
@@ -967,7 +967,7 @@
         <v>56.75</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46156</v>
       </c>
@@ -982,38 +982,38 @@
         <v>60.75</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46157</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="s">
         <v>34</v>
       </c>
       <c r="Q32">
         <f t="shared" si="0"/>
-        <v>61.75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>63.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B37">
         <f>SUM(B3:B32)</f>
-        <v>61.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>63.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>18</v>
       </c>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B62A39-3ED1-43B8-BE76-770EF672A314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFAD49B-942E-46E0-B909-211882998B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>Date</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>Implement Brain FID</t>
+  </si>
+  <si>
+    <t>Running 3_fid with the baseline implementation and with the prof implementation</t>
   </si>
 </sst>
 </file>
@@ -997,23 +1000,34 @@
         <v>63.75</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B37">
-        <f>SUM(B3:B32)</f>
-        <v>63.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <f>SUM(B3:B33)</f>
+        <v>67.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>18</v>
       </c>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFAD49B-942E-46E0-B909-211882998B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E1F4B6-11EE-4515-9756-D62EF5650357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>Date</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>Running 3_fid with the baseline implementation and with the prof implementation</t>
+  </si>
+  <si>
+    <t>Running fid_vis</t>
+  </si>
+  <si>
+    <t>evaluating script, runns, writing prof, bugfixing, running code</t>
   </si>
 </sst>
 </file>
@@ -606,7 +612,7 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q32" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q36" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
@@ -1000,7 +1006,7 @@
         <v>63.75</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46160</v>
       </c>
@@ -1010,24 +1016,58 @@
       <c r="C33" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="Q33">
+        <f t="shared" si="0"/>
+        <v>67.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="0"/>
+        <v>69.75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" si="0"/>
+        <v>77.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B37">
-        <f>SUM(B3:B33)</f>
-        <v>67.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+        <f>SUM(B3:B35)</f>
+        <v>77.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>18</v>
       </c>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uni\6. semester\BA Arbeit\BA\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E1F4B6-11EE-4515-9756-D62EF5650357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F715E99-5E66-4E1C-9F61-4C55E3CF284B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="8775" yWindow="3210" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
   <si>
     <t>Date</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>evaluating script, runns, writing prof, bugfixing, running code</t>
+  </si>
+  <si>
+    <t>Presentation</t>
   </si>
 </sst>
 </file>
@@ -522,13 +525,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -542,7 +545,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -556,7 +559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46091</v>
       </c>
@@ -571,7 +574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46092</v>
       </c>
@@ -586,7 +589,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46093</v>
       </c>
@@ -601,7 +604,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46094</v>
       </c>
@@ -612,11 +615,11 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q36" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q40" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46097</v>
       </c>
@@ -631,7 +634,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46099</v>
       </c>
@@ -646,7 +649,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46100</v>
       </c>
@@ -661,7 +664,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46101</v>
       </c>
@@ -676,7 +679,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46102</v>
       </c>
@@ -691,7 +694,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46103</v>
       </c>
@@ -706,7 +709,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46104</v>
       </c>
@@ -721,7 +724,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46106</v>
       </c>
@@ -736,7 +739,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46108</v>
       </c>
@@ -751,7 +754,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46111</v>
       </c>
@@ -766,7 +769,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46112</v>
       </c>
@@ -781,7 +784,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46113</v>
       </c>
@@ -796,7 +799,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46114</v>
       </c>
@@ -811,7 +814,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46118</v>
       </c>
@@ -826,7 +829,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46119</v>
       </c>
@@ -841,7 +844,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46125</v>
       </c>
@@ -856,7 +859,7 @@
         <v>38.75</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46126</v>
       </c>
@@ -871,7 +874,7 @@
         <v>42.75</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46127</v>
       </c>
@@ -886,7 +889,7 @@
         <v>44.75</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46128</v>
       </c>
@@ -901,7 +904,7 @@
         <v>45.75</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46129</v>
       </c>
@@ -916,7 +919,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46130</v>
       </c>
@@ -931,7 +934,7 @@
         <v>51.75</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46131</v>
       </c>
@@ -946,7 +949,7 @@
         <v>52.75</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46132</v>
       </c>
@@ -961,7 +964,7 @@
         <v>53.75</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46155</v>
       </c>
@@ -976,7 +979,7 @@
         <v>56.75</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46156</v>
       </c>
@@ -991,7 +994,7 @@
         <v>60.75</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46157</v>
       </c>
@@ -1006,7 +1009,7 @@
         <v>63.75</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46160</v>
       </c>
@@ -1021,7 +1024,7 @@
         <v>67.75</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46161</v>
       </c>
@@ -1036,7 +1039,7 @@
         <v>69.75</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46162</v>
       </c>
@@ -1051,24 +1054,84 @@
         <v>77.75</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="0"/>
+        <v>79.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46164</v>
+      </c>
       <c r="B37">
-        <f>SUM(B3:B35)</f>
-        <v>77.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+        <v>1.5</v>
+      </c>
+      <c r="C37" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="0"/>
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="0"/>
+        <v>85.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="0"/>
+        <v>89.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <f>SUM(B3:B39)</f>
+        <v>89.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F715E99-5E66-4E1C-9F61-4C55E3CF284B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56138DA-1A76-4356-86D5-95197206221F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8775" yWindow="3210" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="9120" yWindow="3555" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>Date</t>
   </si>
@@ -1114,10 +1114,25 @@
         <v>89.25</v>
       </c>
     </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="0"/>
+        <v>93.25</v>
+      </c>
+    </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B42">
-        <f>SUM(B3:B39)</f>
-        <v>89.25</v>
+        <f>SUM(B3:B40)</f>
+        <v>93.25</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56138DA-1A76-4356-86D5-95197206221F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7919D0C0-FBEF-47F7-869C-55E7383C1656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9120" yWindow="3555" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="9465" yWindow="3900" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>Date</t>
   </si>
@@ -152,7 +152,10 @@
     <t>evaluating script, runns, writing prof, bugfixing, running code</t>
   </si>
   <si>
-    <t>Presentation</t>
+    <t>Prepare Presentation</t>
+  </si>
+  <si>
+    <t>present practical work</t>
   </si>
 </sst>
 </file>
@@ -615,7 +618,7 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q40" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q41" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
@@ -1129,10 +1132,25 @@
         <v>93.25</v>
       </c>
     </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="0"/>
+        <v>95.25</v>
+      </c>
+    </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B42">
-        <f>SUM(B3:B40)</f>
-        <v>93.25</v>
+        <f>SUM(B3:B41)</f>
+        <v>95.25</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">

--- a/documents/time_log.xlsx
+++ b/documents/time_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\Uni\BA\BA\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7919D0C0-FBEF-47F7-869C-55E7383C1656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17046E39-C5E5-4648-9AE7-AE47003A7229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9465" yWindow="3900" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="28785" windowHeight="11295" xr2:uid="{A4FDAF27-FB63-47E3-8D62-40C01FCADBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
   <si>
     <t>Date</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>present practical work</t>
+  </si>
+  <si>
+    <t>Writing Bachelor thesis</t>
   </si>
 </sst>
 </file>
@@ -528,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCFFE4-CAD8-4510-8E64-539F141A23FF}">
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -618,7 +621,7 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q41" si="0">Q5+B6</f>
+        <f t="shared" ref="Q6:Q42" si="0">Q5+B6</f>
         <v>8.5</v>
       </c>
     </row>
@@ -1148,23 +1151,38 @@
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46177</v>
+      </c>
       <c r="B42">
-        <f>SUM(B3:B41)</f>
-        <v>95.25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="0"/>
+        <v>100.25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <f>SUM(B3:B42)</f>
+        <v>100.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>18</v>
       </c>
     </row>
